--- a/LED_database.xlsx
+++ b/LED_database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8722C61-1095-4484-B6C2-A8C00F41309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A34F214-390F-480C-ADC6-2C5777D93CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="157">
   <si>
     <t>参数</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -823,14 +823,6 @@
 VF：2.8～3.4
 IV：600～1200mcd</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1186,15 +1178,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1209,6 +1192,15 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1499,8 +1491,8 @@
     <col min="4" max="4" width="13" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="27" customWidth="1"/>
-    <col min="8" max="10" width="9" style="27"/>
+    <col min="7" max="7" width="11" style="24" customWidth="1"/>
+    <col min="8" max="10" width="9" style="24"/>
     <col min="11" max="12" width="9" style="1"/>
     <col min="13" max="13" width="12.77734375" style="1" customWidth="1"/>
     <col min="14" max="16" width="9" style="1"/>
@@ -1515,13 +1507,13 @@
   <sheetData>
     <row r="1" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>1</v>
@@ -1530,42 +1522,42 @@
         <v>2</v>
       </c>
       <c r="F1" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="H1" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>142</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>144</v>
       </c>
       <c r="K1" s="17" t="s">
         <v>3</v>
       </c>
       <c r="L1" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="N1" s="23"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="25"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="30"/>
     </row>
     <row r="2" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
@@ -1582,23 +1574,23 @@
       <c r="F2" s="21">
         <v>1001</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="24">
         <v>0.6956</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="26">
         <v>0.30309999999999998</v>
       </c>
-      <c r="I2" s="29">
+      <c r="I2" s="26">
         <v>0.53039999999999998</v>
       </c>
-      <c r="J2" s="29">
+      <c r="J2" s="26">
         <v>0.34660000000000002</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>4</v>
@@ -1628,23 +1620,23 @@
       <c r="F3" s="21">
         <v>1001</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="24">
         <v>0.6512</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="26">
         <v>0.34460000000000002</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="26">
         <v>0.44650000000000001</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="26">
         <v>0.35449999999999998</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>6</v>
@@ -1674,23 +1666,23 @@
       <c r="F4" s="21">
         <v>1001</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="24">
         <v>0.69620000000000004</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="26">
         <v>0.30320000000000003</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="26">
         <v>0.53190000000000004</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="26">
         <v>0.34649999999999997</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>4</v>
@@ -1720,23 +1712,23 @@
       <c r="F5" s="21">
         <v>1040</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="24">
         <v>0.64739999999999998</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="26">
         <v>0.34989999999999999</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="26">
         <v>0.43859999999999999</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="26">
         <v>0.35560000000000003</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>4</v>
@@ -1766,23 +1758,23 @@
       <c r="F6" s="21">
         <v>1001</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="24">
         <v>0.69610000000000005</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="26">
         <v>0.30230000000000001</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="26">
         <v>0.53180000000000005</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="26">
         <v>0.34649999999999997</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>4</v>
@@ -1812,23 +1804,23 @@
       <c r="F7" s="21">
         <v>1001</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="24">
         <v>0.65339999999999998</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="26">
         <v>0.34410000000000002</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="26">
         <v>0.44890000000000002</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="26">
         <v>0.35460000000000003</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>11</v>
@@ -1858,23 +1850,23 @@
       <c r="F8" s="21">
         <v>1027</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="24">
         <v>0.64959999999999996</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="26">
         <v>0.34849999999999998</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="26">
         <v>0.44169999999999998</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="26">
         <v>0.35539999999999999</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>11</v>
@@ -1904,23 +1896,23 @@
       <c r="F9" s="21">
         <v>6846</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="24">
         <v>0.25359999999999999</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="26">
         <v>0.61880000000000002</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="26">
         <v>0.1023</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="26">
         <v>0.37430000000000002</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>6</v>
@@ -1950,23 +1942,23 @@
       <c r="F10" s="21">
         <v>7003</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="24">
         <v>0.25340000000000001</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="26">
         <v>0.57840000000000003</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="26">
         <v>0.1074</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="26">
         <v>0.3679</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -1996,23 +1988,23 @@
       <c r="F11" s="21">
         <v>7311</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="24">
         <v>0.19570000000000001</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="26">
         <v>0.75180000000000002</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="26">
         <v>6.7299999999999999E-2</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="26">
         <v>0.38790000000000002</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>4</v>
@@ -2042,23 +2034,23 @@
       <c r="F12" s="21">
         <v>7463</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="24">
         <v>0.18240000000000001</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="26">
         <v>0.76149999999999995</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="26">
         <v>6.2E-2</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="26">
         <v>0.3881</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>4</v>
@@ -2088,23 +2080,23 @@
       <c r="F13" s="21">
         <v>7454</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="24">
         <v>0.183</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="26">
         <v>0.76100000000000001</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="26">
         <v>6.2199999999999998E-2</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="26">
         <v>0.3881</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>4</v>
@@ -2134,23 +2126,23 @@
       <c r="F14" s="21">
         <v>2793</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="24">
         <v>0.48970000000000002</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="26">
         <v>0.4783</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="26">
         <v>0.25240000000000001</v>
       </c>
-      <c r="J14" s="29">
+      <c r="J14" s="26">
         <v>0.36980000000000002</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>4</v>
@@ -2180,23 +2172,23 @@
       <c r="F15" s="21">
         <v>1783</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="24">
         <v>0.56489999999999996</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="26">
         <v>0.42430000000000001</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="26">
         <v>0.3246</v>
       </c>
-      <c r="J15" s="29">
+      <c r="J15" s="26">
         <v>0.36570000000000003</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>4</v>
@@ -2226,23 +2218,23 @@
       <c r="F16" s="21">
         <v>2078</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="24">
         <v>0.54359999999999997</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="26">
         <v>0.44929999999999998</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="26">
         <v>0.29770000000000002</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="26">
         <v>0.36909999999999998</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>23</v>
@@ -2272,23 +2264,23 @@
       <c r="F17" s="21">
         <v>2848</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="24">
         <v>0.47049999999999997</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="26">
         <v>0.45029999999999998</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="26">
         <v>0.25219999999999998</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="26">
         <v>0.36199999999999999</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>4</v>
@@ -2318,23 +2310,23 @@
       <c r="F18" s="21">
         <v>2817</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="24">
         <v>0.47349999999999998</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="26">
         <v>0.45190000000000002</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="26">
         <v>0.25330000000000003</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="26">
         <v>0.36270000000000002</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>44</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>4</v>
@@ -2364,23 +2356,23 @@
       <c r="F19" s="21">
         <v>9232</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="24">
         <v>0.28570000000000001</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="26">
         <v>0.29310000000000003</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="26">
         <v>0.19220000000000001</v>
       </c>
-      <c r="J19" s="29">
+      <c r="J19" s="26">
         <v>0.29580000000000001</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -2413,23 +2405,23 @@
       <c r="F20" s="21">
         <v>10192</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="24">
         <v>0.27760000000000001</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="26">
         <v>0.29099999999999998</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="26">
         <v>0.18709999999999999</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="26">
         <v>0.29409999999999997</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>4</v>
@@ -2459,23 +2451,23 @@
       <c r="F21" s="21">
         <v>13774</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="24">
         <v>0.26700000000000002</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="26">
         <v>0.27039999999999997</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="26">
         <v>0.187</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="26">
         <v>0.28410000000000002</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>4</v>
@@ -2505,23 +2497,23 @@
       <c r="F22" s="21">
         <v>13363</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="24">
         <v>0.27</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="26">
         <v>0.26910000000000001</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="26">
         <v>0.1898</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="26">
         <v>0.2838</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>4</v>
@@ -2554,23 +2546,23 @@
       <c r="F23" s="21">
         <v>10942</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="24">
         <v>0.27</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="26">
         <v>0.26919999999999999</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="26">
         <v>0.1898</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="26">
         <v>0.28389999999999999</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>11</v>
@@ -2603,23 +2595,23 @@
       <c r="F24" s="21">
         <v>3613</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="24">
         <v>0.40029999999999999</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="26">
         <v>0.39090000000000003</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="26">
         <v>0.2324</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="26">
         <v>0.34039999999999998</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>23</v>
@@ -2649,23 +2641,23 @@
       <c r="F25" s="21">
         <v>10206</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="24">
         <v>0.27560000000000001</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="26">
         <v>0.29459999999999997</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="26">
         <v>0.1842</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="26">
         <v>0.2954</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>73</v>
@@ -2695,23 +2687,23 @@
       <c r="F26" s="21">
         <v>9366</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="24">
         <v>0.27889999999999998</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="26">
         <v>0.3049</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="26">
         <v>0.18290000000000001</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="26">
         <v>0.2999</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>73</v>
@@ -2741,23 +2733,23 @@
       <c r="F27" s="21">
         <v>8386</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="24">
         <v>0.28639999999999999</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="26">
         <v>0.316</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="26">
         <v>0.1842</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="26">
         <v>0.3049</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>79</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>73</v>
@@ -2787,23 +2779,23 @@
       <c r="F28" s="21">
         <v>2837</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="24">
         <v>0.46899999999999997</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="26">
         <v>0.4461</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="26">
         <v>0.253</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="26">
         <v>0.36099999999999999</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>73</v>
@@ -2833,23 +2825,23 @@
       <c r="F29" s="21">
         <v>2804</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="24">
         <v>0.47499999999999998</v>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="26">
         <v>0.45300000000000001</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="26">
         <v>0.25380000000000003</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="26">
         <v>0.36309999999999998</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>85</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>73</v>
@@ -2879,23 +2871,23 @@
       <c r="F30" s="21">
         <v>4882</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="24">
         <v>0.35299999999999998</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="26">
         <v>0.39500000000000002</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="26">
         <v>0.20069999999999999</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="26">
         <v>0.33689999999999998</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>73</v>
@@ -2925,23 +2917,23 @@
       <c r="F31" s="21">
         <v>5210</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="24">
         <v>0.3412</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="26">
         <v>0.38069999999999998</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="26">
         <v>0.19800000000000001</v>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="26">
         <v>0.33169999999999999</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>73</v>
@@ -2971,23 +2963,23 @@
       <c r="F32" s="21">
         <v>2912</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="24">
         <v>0.44350000000000001</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="26">
         <v>0.40660000000000002</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="26">
         <v>0.25369999999999998</v>
       </c>
-      <c r="J32" s="29">
+      <c r="J32" s="26">
         <v>0.34889999999999999</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>93</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>11</v>
@@ -3017,23 +3009,23 @@
       <c r="F33" s="21">
         <v>3123</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="24">
         <v>0.43099999999999999</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="26">
         <v>0.40660000000000002</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="26">
         <v>0.2457</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="26">
         <v>0.34760000000000002</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>95</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>11</v>
@@ -3063,23 +3055,23 @@
       <c r="F34" s="21">
         <v>2815</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="24">
         <v>0.46339999999999998</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="26">
         <v>0.4325</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="26">
         <v>0.25519999999999998</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J34" s="26">
         <v>0.35730000000000001</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>98</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>11</v>
@@ -3109,23 +3101,23 @@
       <c r="F35" s="21">
         <v>5005</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="24">
         <v>0.3458</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="26">
         <v>0.3609</v>
       </c>
-      <c r="I35" s="29">
+      <c r="I35" s="26">
         <v>0.20830000000000001</v>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="26">
         <v>0.3261</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>105</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>99</v>
@@ -3155,23 +3147,23 @@
       <c r="F36" s="21">
         <v>5004</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="24">
         <v>0.34670000000000001</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="26">
         <v>0.37169999999999997</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="26">
         <v>0.20499999999999999</v>
       </c>
-      <c r="J36" s="29">
+      <c r="J36" s="26">
         <v>0.3296</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>108</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>11</v>
@@ -3201,23 +3193,23 @@
       <c r="F37" s="21">
         <v>6300</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="24">
         <v>0.315</v>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="26">
         <v>0.34260000000000002</v>
       </c>
-      <c r="I37" s="29">
+      <c r="I37" s="26">
         <v>0.19439999999999999</v>
       </c>
-      <c r="J37" s="29">
+      <c r="J37" s="26">
         <v>0.31719999999999998</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>11</v>
@@ -3247,23 +3239,23 @@
       <c r="F38" s="21">
         <v>6341</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="24">
         <v>0.31440000000000001</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="26">
         <v>0.34089999999999998</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="26">
         <v>0.1946</v>
       </c>
-      <c r="J38" s="29">
+      <c r="J38" s="26">
         <v>0.3165</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>4</v>
@@ -3293,23 +3285,23 @@
       <c r="F39" s="21">
         <v>5538</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="24">
         <v>0.33169999999999999</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="26">
         <v>0.36009999999999998</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="26">
         <v>0.1993</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="26">
         <v>0.32450000000000001</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>116</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>4</v>
@@ -3339,23 +3331,23 @@
       <c r="F40" s="21">
         <v>5104</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="24">
         <v>0.34320000000000001</v>
       </c>
-      <c r="H40" s="29">
+      <c r="H40" s="26">
         <v>0.36299999999999999</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="26">
         <v>0.20580000000000001</v>
       </c>
-      <c r="J40" s="29">
+      <c r="J40" s="26">
         <v>0.32650000000000001</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>119</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>4</v>
@@ -3385,23 +3377,23 @@
       <c r="F41" s="21">
         <v>100000</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="24">
         <v>0.12239999999999999</v>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="26">
         <v>7.85E-2</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="26">
         <v>0.13250000000000001</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="26">
         <v>0.12740000000000001</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>122</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>11</v>
@@ -3431,23 +3423,23 @@
       <c r="F42" s="21">
         <v>100000</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="24">
         <v>0.13539999999999999</v>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="26">
         <v>5.0099999999999999E-2</v>
       </c>
-      <c r="I42" s="29">
+      <c r="I42" s="26">
         <v>0.16259999999999999</v>
       </c>
-      <c r="J42" s="29">
+      <c r="J42" s="26">
         <v>9.0300000000000005E-2</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>125</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>126</v>
@@ -3477,23 +3469,23 @@
       <c r="F43" s="21">
         <v>9036</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="24">
         <v>0.28310000000000002</v>
       </c>
-      <c r="H43" s="29">
+      <c r="H43" s="26">
         <v>0.30370000000000003</v>
       </c>
-      <c r="I43" s="29">
+      <c r="I43" s="26">
         <v>0.18629999999999999</v>
       </c>
-      <c r="J43" s="29">
+      <c r="J43" s="26">
         <v>0.29980000000000001</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>128</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>73</v>
@@ -3523,23 +3515,23 @@
       <c r="F44" s="21">
         <v>10308</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="24">
         <v>0.2777</v>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="26">
         <v>0.28889999999999999</v>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="26">
         <v>0.18790000000000001</v>
       </c>
-      <c r="J44" s="29">
+      <c r="J44" s="26">
         <v>0.29320000000000002</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>131</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>73</v>
@@ -3563,29 +3555,29 @@
       <c r="D45" s="21">
         <v>232.56</v>
       </c>
-      <c r="E45" s="21" t="s">
-        <v>136</v>
+      <c r="E45" s="21">
+        <v>0</v>
       </c>
       <c r="F45" s="21">
         <v>8356</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="24">
         <v>0.28870000000000001</v>
       </c>
-      <c r="H45" s="29">
+      <c r="H45" s="26">
         <v>0.31040000000000001</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="26">
         <v>0.18790000000000001</v>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="26">
         <v>0.30299999999999999</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N45" s="10"/>
       <c r="P45" s="3"/>
@@ -3606,30 +3598,30 @@
       <c r="D46" s="22">
         <v>244.39</v>
       </c>
-      <c r="E46" s="22" t="s">
-        <v>137</v>
+      <c r="E46" s="22">
+        <v>0</v>
       </c>
       <c r="F46" s="22">
         <v>8402</v>
       </c>
-      <c r="G46" s="28">
+      <c r="G46" s="25">
         <v>0.2883</v>
       </c>
-      <c r="H46" s="30">
+      <c r="H46" s="27">
         <v>0.30980000000000002</v>
       </c>
-      <c r="I46" s="30">
+      <c r="I46" s="27">
         <v>0.18779999999999999</v>
       </c>
-      <c r="J46" s="30">
+      <c r="J46" s="27">
         <v>0.30270000000000002</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="7"/>
@@ -3642,7 +3634,7 @@
       <c r="V46" s="8"/>
     </row>
     <row r="1048576" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H1048576" s="27">
+      <c r="H1048576" s="24">
         <f>MIN(H45:H1048575)</f>
         <v>0.30980000000000002</v>
       </c>
